--- a/files/04-bad-metadata.xlsx
+++ b/files/04-bad-metadata.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\ed-dash\fair-bio-practice\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/s2531396/Documents/GitHub/fair-in-circadian-practice/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE580A3F-8C8F-A94E-B53B-14E52D84347B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22935" yWindow="1545" windowWidth="23250" windowHeight="12570"/>
+    <workbookView xWindow="30240" yWindow="0" windowWidth="38400" windowHeight="24000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Intro" sheetId="1" r:id="rId1"/>
@@ -19,14 +20,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -318,10 +311,6 @@
     <t>C5</t>
   </si>
   <si>
-    <t xml:space="preserve">Biomas
-</t>
-  </si>
-  <si>
     <t>0.1206g</t>
   </si>
   <si>
@@ -471,12 +460,15 @@
   </si>
   <si>
     <t>Cell</t>
+  </si>
+  <si>
+    <t>Biomass</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yy\-mm\-dd;@"/>
   </numFmts>
@@ -597,7 +589,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -654,8 +646,6 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -989,73 +979,56 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="6" max="6" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31" t="s">
+      <c r="D1" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="C2" s="31"/>
+      <c r="B2" t="s">
+        <v>117</v>
+      </c>
       <c r="D2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>113</v>
       </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-    </row>
-    <row r="4" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="31"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="41" t="s">
-        <v>117</v>
-      </c>
-      <c r="H4" s="43" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G4" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="H4" s="41" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>2</v>
@@ -1064,27 +1037,27 @@
         <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G5" s="42"/>
-      <c r="H5" s="43"/>
+        <v>87</v>
+      </c>
+      <c r="G5" s="40"/>
+      <c r="H5" s="41"/>
       <c r="J5" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>0</v>
       </c>
       <c r="L5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M5" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="M5" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="17" t="s">
         <v>3</v>
       </c>
@@ -1098,7 +1071,7 @@
         <v>25</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F6" s="18">
         <v>6</v>
@@ -1107,13 +1080,13 @@
         <v>1.2</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J6" t="s">
         <v>3</v>
       </c>
       <c r="K6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L6" s="18">
         <v>24.2</v>
@@ -1122,7 +1095,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="17" t="s">
         <v>4</v>
       </c>
@@ -1136,7 +1109,7 @@
         <v>25</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F7" s="18">
         <v>6.5</v>
@@ -1151,7 +1124,7 @@
         <v>4</v>
       </c>
       <c r="K7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L7" s="18">
         <v>23.5</v>
@@ -1160,7 +1133,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
         <v>5</v>
       </c>
@@ -1174,7 +1147,7 @@
         <v>25</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F8" s="18">
         <v>5</v>
@@ -1189,7 +1162,7 @@
         <v>5</v>
       </c>
       <c r="K8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L8" s="18">
         <v>24.5</v>
@@ -1198,36 +1171,36 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="32" t="s">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="33" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" s="33">
+      <c r="E9" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" s="31">
         <v>3</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="31">
         <v>0.6</v>
       </c>
-      <c r="H9" s="33">
+      <c r="H9" s="31">
         <v>2E-3</v>
       </c>
       <c r="J9" t="s">
         <v>6</v>
       </c>
       <c r="K9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L9" s="8">
         <v>27.1</v>
@@ -1236,36 +1209,36 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="F10" s="33">
+      <c r="E10" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="31">
         <v>0</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="31">
         <v>1.1000000000000001</v>
       </c>
-      <c r="H10" s="33">
+      <c r="H10" s="31">
         <v>1.6999999999999999E-3</v>
       </c>
       <c r="J10" t="s">
         <v>20</v>
       </c>
       <c r="K10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L10" s="8">
         <v>30.1</v>
@@ -1274,7 +1247,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="23" t="s">
         <v>7</v>
       </c>
@@ -1303,7 +1276,7 @@
         <v>7</v>
       </c>
       <c r="K11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L11" s="18">
         <v>24.5</v>
@@ -1312,7 +1285,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="23" t="s">
         <v>8</v>
       </c>
@@ -1341,7 +1314,7 @@
         <v>8</v>
       </c>
       <c r="K12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L12" s="18">
         <v>24.1</v>
@@ -1350,7 +1323,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="23" t="s">
         <v>9</v>
       </c>
@@ -1364,7 +1337,7 @@
         <v>26</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F13" s="24">
         <v>5.8</v>
@@ -1373,13 +1346,13 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J13" t="s">
         <v>9</v>
       </c>
       <c r="K13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L13" s="18">
         <v>25</v>
@@ -1388,7 +1361,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="23" t="s">
         <v>10</v>
       </c>
@@ -1402,7 +1375,7 @@
         <v>26</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F14" s="24">
         <v>4.9000000000000004</v>
@@ -1417,16 +1390,16 @@
         <v>10</v>
       </c>
       <c r="K14" t="s">
-        <v>85</v>
-      </c>
-      <c r="L14" s="30">
+        <v>84</v>
+      </c>
+      <c r="L14">
         <v>-1</v>
       </c>
       <c r="M14">
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="23" t="s">
         <v>21</v>
       </c>
@@ -1440,7 +1413,7 @@
         <v>26</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F15" s="24">
         <v>5.9</v>
@@ -1455,7 +1428,7 @@
         <v>21</v>
       </c>
       <c r="K15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L15" s="8">
         <v>31.1</v>
@@ -1464,7 +1437,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
         <v>64</v>
       </c>
@@ -1472,13 +1445,13 @@
         <v>11</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F16" s="18">
         <v>6</v>
@@ -1490,7 +1463,7 @@
         <v>1.8E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="17" t="s">
         <v>65</v>
       </c>
@@ -1498,13 +1471,13 @@
         <v>12</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F17" s="18">
         <v>6.5</v>
@@ -1516,7 +1489,7 @@
         <v>1.6000000000000001E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="17" t="s">
         <v>66</v>
       </c>
@@ -1524,13 +1497,13 @@
         <v>13</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F18" s="18">
         <v>5</v>
@@ -1542,7 +1515,7 @@
         <v>1.4E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="17" t="s">
         <v>67</v>
       </c>
@@ -1550,13 +1523,13 @@
         <v>14</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F19" s="18">
         <v>3</v>
@@ -1568,7 +1541,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="17" t="s">
         <v>68</v>
       </c>
@@ -1576,13 +1549,13 @@
         <v>15</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F20" s="18"/>
       <c r="G20" s="18">
@@ -1592,21 +1565,21 @@
         <v>1.6999999999999999E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
         <v>13</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="D21" s="39" t="s">
-        <v>109</v>
+      <c r="C21" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="37" t="s">
+        <v>108</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F21" s="8">
         <v>6</v>
@@ -1618,41 +1591,41 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B22" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" s="37" t="s">
-        <v>109</v>
+      <c r="C22" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" s="35" t="s">
+        <v>108</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F22" s="22"/>
       <c r="G22" s="22"/>
       <c r="H22" s="22"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>109</v>
+      <c r="C23" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="37" t="s">
+        <v>108</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F23" s="8">
         <v>7</v>
@@ -1664,21 +1637,21 @@
         <v>2.0999999999999999E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" s="39" t="s">
-        <v>109</v>
+      <c r="C24" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" s="37" t="s">
+        <v>108</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F24" s="8">
         <v>3.1</v>
@@ -1690,21 +1663,21 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" s="39" t="s">
-        <v>109</v>
+      <c r="C25" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="D25" s="37" t="s">
+        <v>108</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F25" s="8">
         <v>5</v>
@@ -1716,9 +1689,9 @@
         <v>1.1000000000000001E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B26" s="20" t="s">
         <v>43</v>
@@ -1726,22 +1699,22 @@
       <c r="C26" s="20"/>
       <c r="D26" s="6"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B27" s="24" t="s">
         <v>42</v>
       </c>
       <c r="C27" s="24"/>
       <c r="E27" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="F27" s="40">
+        <v>115</v>
+      </c>
+      <c r="F27" s="38">
         <v>44419</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="5"/>
     </row>
   </sheetData>
@@ -1755,21 +1728,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="1" max="1" width="24.1640625" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.5" customWidth="1"/>
+    <col min="5" max="5" width="14.1640625" customWidth="1"/>
     <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.28515625" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" customWidth="1"/>
+    <col min="8" max="8" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" customWidth="1"/>
+    <col min="10" max="10" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
@@ -1783,7 +1756,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>46</v>
       </c>
@@ -1792,7 +1765,7 @@
       </c>
       <c r="C2" s="7"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>30</v>
       </c>
@@ -1809,7 +1782,7 @@
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>57</v>
       </c>
@@ -1819,7 +1792,7 @@
       <c r="C4" s="7"/>
       <c r="F4" s="3"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>31</v>
       </c>
@@ -1829,7 +1802,7 @@
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>32</v>
       </c>
@@ -1841,7 +1814,7 @@
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>49</v>
       </c>
@@ -1862,7 +1835,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -1894,7 +1867,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>3</v>
       </c>
@@ -1926,7 +1899,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>4</v>
       </c>
@@ -1958,7 +1931,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>5</v>
       </c>
@@ -1990,7 +1963,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>6</v>
       </c>
@@ -2022,7 +1995,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>20</v>
       </c>
@@ -2054,7 +2027,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>7</v>
       </c>
@@ -2086,7 +2059,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>8</v>
       </c>
@@ -2118,7 +2091,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>9</v>
       </c>
@@ -2150,7 +2123,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>10</v>
       </c>
@@ -2182,7 +2155,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>21</v>
       </c>
@@ -2214,10 +2187,10 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="4"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="13" t="s">
         <v>22</v>
       </c>
@@ -2232,7 +2205,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="13" t="s">
         <v>23</v>
       </c>
@@ -2241,7 +2214,7 @@
       </c>
       <c r="C21" s="9"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="14" t="s">
         <v>33</v>
       </c>
